--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.87336</v>
+        <v>16.80107</v>
       </c>
       <c r="D2" t="n">
-        <v>16.547</v>
+        <v>16.38308</v>
       </c>
       <c r="E2" t="n">
-        <v>16.69215</v>
+        <v>16.45355</v>
       </c>
       <c r="F2" t="n">
-        <v>42.31161</v>
+        <v>43.18655</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05066</v>
+        <v>0.05046</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79897</v>
+        <v>1.83567</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.83511</v>
+        <v>16.94268</v>
       </c>
       <c r="D3" t="n">
-        <v>16.48423</v>
+        <v>16.42088</v>
       </c>
       <c r="E3" t="n">
-        <v>16.78264</v>
+        <v>16.80217</v>
       </c>
       <c r="F3" t="n">
-        <v>42.13658</v>
+        <v>42.86181</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05129</v>
+        <v>0.05142</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83586</v>
+        <v>1.80606</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.75245</v>
+        <v>16.91915</v>
       </c>
       <c r="D4" t="n">
-        <v>16.56098</v>
+        <v>16.43733</v>
       </c>
       <c r="E4" t="n">
-        <v>16.42862</v>
+        <v>16.79374</v>
       </c>
       <c r="F4" t="n">
-        <v>42.94114</v>
+        <v>42.52571</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05006</v>
+        <v>0.04991</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82966</v>
+        <v>1.86308</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.68075</v>
+        <v>16.69209</v>
       </c>
       <c r="D6" t="n">
-        <v>15.63357</v>
+        <v>15.96209</v>
       </c>
       <c r="E6" t="n">
-        <v>16.52626</v>
+        <v>16.47125</v>
       </c>
       <c r="F6" t="n">
-        <v>21.95659</v>
+        <v>22.20417</v>
       </c>
       <c r="G6" t="n">
-        <v>34.46866</v>
+        <v>33.49429</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.67844</v>
+        <v>16.51334</v>
       </c>
       <c r="D7" t="n">
-        <v>15.7996</v>
+        <v>15.76477</v>
       </c>
       <c r="E7" t="n">
-        <v>16.31843</v>
+        <v>16.46892</v>
       </c>
       <c r="F7" t="n">
-        <v>22.05619</v>
+        <v>21.69805</v>
       </c>
       <c r="G7" t="n">
-        <v>34.07233</v>
+        <v>34.57736</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.81219</v>
+        <v>16.54575</v>
       </c>
       <c r="D8" t="n">
-        <v>15.96033</v>
+        <v>15.99572</v>
       </c>
       <c r="E8" t="n">
-        <v>16.80363</v>
+        <v>16.33843</v>
       </c>
       <c r="F8" t="n">
-        <v>21.87032</v>
+        <v>21.70613</v>
       </c>
       <c r="G8" t="n">
-        <v>34.62682</v>
+        <v>33.8496</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60495</v>
+        <v>0.61198</v>
       </c>
       <c r="D10" t="n">
-        <v>1.09384</v>
+        <v>1.10037</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60315</v>
+        <v>0.60265</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11682</v>
+        <v>1.12199</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60948</v>
+        <v>0.60508</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1176</v>
+        <v>1.11924</v>
       </c>
     </row>
   </sheetData>
